--- a/src/fastcashflow/sample_data/sample_vfa_basis.xlsx
+++ b/src/fastcashflow/sample_data/sample_vfa_basis.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,70 +471,80 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>product_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>channel_code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>channel_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>mortality_table</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>lapse_table</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>waiver_table</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>discount_table</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>inflation_table</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ra_confidence</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>mortality_cv</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>morbidity_cv</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>state_model</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>surrender_value_table</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>expense_table</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>investment_return</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>fund_fee</t>
         </is>
@@ -546,41 +556,41 @@
           <t>defaults</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>MORTALITY_STD</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>WAIVER_STD</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>DISCOUNT_STD</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>INFL_BASE</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.75</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>0.1</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.12</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>WAIVER</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>SURRENDER_STD</t>
         </is>
@@ -594,23 +604,33 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>변액연금</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>BANCA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>방카슈랑스</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>LAPSE_FC</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>EXP_TE_FC</t>
         </is>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.05</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.015</v>
       </c>
     </row>

--- a/src/fastcashflow/sample_data/sample_vfa_basis.xlsx
+++ b/src/fastcashflow/sample_data/sample_vfa_basis.xlsx
@@ -29813,7 +29813,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>defaults</t>
+          <t>_DEFAULTS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/src/fastcashflow/sample_data/sample_vfa_basis.xlsx
+++ b/src/fastcashflow/sample_data/sample_vfa_basis.xlsx
@@ -421,91 +421,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>product_code</t>
+          <t>product</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>product_name</t>
+          <t>channel</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>channel_code</t>
+          <t>mortality_table</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>channel_name</t>
+          <t>lapse_table</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>mortality_table</t>
+          <t>waiver_table</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>lapse_table</t>
+          <t>discount_table</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>waiver_table</t>
+          <t>inflation_table</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>discount_table</t>
+          <t>ra_confidence</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>inflation_table</t>
+          <t>mortality_cv</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>ra_confidence</t>
+          <t>morbidity_cv</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>mortality_cv</t>
+          <t>state_model</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>morbidity_cv</t>
+          <t>surrender_value_table</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>state_model</t>
+          <t>expense_table</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>surrender_value_table</t>
+          <t>investment_return</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
-        <is>
-          <t>expense_table</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>investment_return</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
         <is>
           <t>fund_fee</t>
         </is>
@@ -517,59 +507,59 @@
           <t>_DEFAULTS</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MORTALITY_STD</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LAPSE_VFA</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MORTALITY_STD</t>
+          <t>WAIVER_STD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LAPSE_VFA</t>
+          <t>DISCOUNT_STD</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>WAIVER_STD</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>DISCOUNT_STD</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
           <t>INFL_BASE</t>
         </is>
       </c>
+      <c r="H2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1</v>
+      </c>
       <c r="J2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L2" t="n">
         <v>0.12</v>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>WAIVER</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>SURR_HEALTH</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>WAIVER</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>SURR_HEALTH</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
           <t>EXP_HE_GA</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="N2" t="n">
         <v>0.05</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="O2" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -581,17 +571,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>변액연금</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
           <t>BANCA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>방카슈랑스</t>
         </is>
       </c>
     </row>

--- a/src/fastcashflow/sample_data/sample_vfa_basis.xlsx
+++ b/src/fastcashflow/sample_data/sample_vfa_basis.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>EXP_HE_GA</t>
+          <t>EXPENSE_HEALTH_GA</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -74139,7 +74139,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EXP_TE_FC</t>
+          <t>EXPENSE_TERM_FC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -74159,7 +74159,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EXP_TE_FC</t>
+          <t>EXPENSE_TERM_FC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -74179,7 +74179,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EXP_TE_GA</t>
+          <t>EXPENSE_TERM_GA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -74199,7 +74199,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EXP_TE_GA</t>
+          <t>EXPENSE_TERM_GA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -74219,7 +74219,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EXP_HE_FC</t>
+          <t>EXPENSE_HEALTH_FC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -74239,7 +74239,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EXP_HE_FC</t>
+          <t>EXPENSE_HEALTH_FC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -74259,7 +74259,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EXP_HE_GA</t>
+          <t>EXPENSE_HEALTH_GA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -74279,7 +74279,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXP_HE_GA</t>
+          <t>EXPENSE_HEALTH_GA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -74299,7 +74299,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXP_HE_TM</t>
+          <t>EXPENSE_HEALTH_TM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -74319,7 +74319,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXP_HE_TM</t>
+          <t>EXPENSE_HEALTH_TM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -74339,7 +74339,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXP_WH_FC</t>
+          <t>EXPENSE_WHOLE_FC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -74359,7 +74359,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EXP_WH_FC</t>
+          <t>EXPENSE_WHOLE_FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -74379,7 +74379,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXP_WH_GA</t>
+          <t>EXPENSE_WHOLE_GA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -74399,7 +74399,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EXP_WH_GA</t>
+          <t>EXPENSE_WHOLE_GA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/src/fastcashflow/sample_data/sample_vfa_basis.xlsx
+++ b/src/fastcashflow/sample_data/sample_vfa_basis.xlsx
@@ -74122,12 +74122,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>expense_type</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>basis</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -74149,7 +74149,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>alpha_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -74169,7 +74169,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gamma_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -74189,7 +74189,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>alpha_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -74209,7 +74209,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gamma_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -74229,7 +74229,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>alpha_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -74249,7 +74249,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gamma_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -74269,7 +74269,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>alpha_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -74289,7 +74289,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gamma_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -74309,7 +74309,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>alpha_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -74329,7 +74329,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gamma_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -74349,7 +74349,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>alpha_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -74369,7 +74369,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>gamma_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -74389,7 +74389,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>alpha_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -74409,7 +74409,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gamma_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D15" t="n">

--- a/src/fastcashflow/sample_data/sample_vfa_basis.xlsx
+++ b/src/fastcashflow/sample_data/sample_vfa_basis.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>WAIVER</t>
+          <t>ACTIVE_WAIVER</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">

--- a/src/fastcashflow/sample_data/sample_vfa_basis.xlsx
+++ b/src/fastcashflow/sample_data/sample_vfa_basis.xlsx
@@ -477,7 +477,7 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>state_model</t>
+          <t>state_machine</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
